--- a/data/trans_orig/P57B1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B1_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido deprimido en 2023</t>
+          <t>Población según se ha sentido deprimido en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17826</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24283</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30852</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27602</t>
+          <t>28243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49569</t>
+          <t>50154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>133396</t>
+          <t>133114</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>176401</t>
+          <t>177741</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>114099</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>147000</t>
+          <t>146837</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257413</t>
+          <t>257139</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>311211</t>
+          <t>310524</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>304704</t>
+          <t>301390</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>347631</t>
+          <t>346508</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270908</t>
+          <t>272414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>305187</t>
+          <t>306611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>589222</t>
+          <t>586374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>644144</t>
+          <t>643238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,59%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15228</t>
+          <t>15527</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34251</t>
+          <t>33264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17785</t>
+          <t>17550</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35929</t>
+          <t>37138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37069</t>
+          <t>37324</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62807</t>
+          <t>62905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118768</t>
+          <t>121658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158499</t>
+          <t>161113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117399</t>
+          <t>117021</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149449</t>
+          <t>149823</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248450</t>
+          <t>249759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>300354</t>
+          <t>298872</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>263820</t>
+          <t>262117</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>304318</t>
+          <t>303849</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>201550</t>
+          <t>200657</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>234437</t>
+          <t>233585</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>473700</t>
+          <t>474608</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>527613</t>
+          <t>527648</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15284</t>
+          <t>14795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21379</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>9686</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49628</t>
+          <t>49862</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>20772</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64015</t>
+          <t>64797</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45271</t>
+          <t>49081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>198716</t>
+          <t>202364</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46490</t>
+          <t>47265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65633</t>
+          <t>65989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81194</t>
+          <t>67768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>260482</t>
+          <t>262952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>412125</t>
+          <t>408415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>606015</t>
+          <t>602657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80628</t>
+          <t>80523</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100931</t>
+          <t>100310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>497271</t>
+          <t>492860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>728785</t>
+          <t>742788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19179</t>
+          <t>19684</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39950</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27301</t>
+          <t>26725</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30764</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58456</t>
+          <t>58853</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53023</t>
+          <t>51119</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82426</t>
+          <t>82001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26340</t>
+          <t>24344</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68600</t>
+          <t>69151</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78827</t>
+          <t>80692</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>138817</t>
+          <t>140041</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>275634</t>
+          <t>271878</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>334587</t>
+          <t>334442</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>293840</t>
+          <t>299160</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>668590</t>
+          <t>712288</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>597549</t>
+          <t>594113</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1132641</t>
+          <t>1133189</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,4%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>598455</t>
+          <t>599651</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>670490</t>
+          <t>668061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>264643</t>
+          <t>230804</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>596471</t>
+          <t>591204</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>763798</t>
+          <t>765693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1233911</t>
+          <t>1238801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>28105</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29010</t>
+          <t>29205</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53787</t>
+          <t>54909</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46496</t>
+          <t>44649</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>73705</t>
+          <t>74479</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26381</t>
+          <t>26180</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47170</t>
+          <t>46867</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60374</t>
+          <t>61796</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>99747</t>
+          <t>100757</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>94816</t>
+          <t>96171</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138455</t>
+          <t>138161</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>132657</t>
+          <t>134563</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>177058</t>
+          <t>174992</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>213920</t>
+          <t>208318</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>334961</t>
+          <t>334177</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>370190</t>
+          <t>366323</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>491925</t>
+          <t>491348</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>241989</t>
+          <t>244145</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>288667</t>
+          <t>287226</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>366628</t>
+          <t>366790</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>537861</t>
+          <t>536042</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>634058</t>
+          <t>631908</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>802731</t>
+          <t>807341</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,53%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>498</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28793</t>
+          <t>28797</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>16778</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30393</t>
+          <t>32070</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20785</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>63720</t>
+          <t>63774</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>91347</t>
+          <t>91321</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>71251</t>
+          <t>69276</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>102942</t>
+          <t>104004</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22521</t>
+          <t>22511</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>56173</t>
+          <t>56829</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>270228</t>
+          <t>268613</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>319846</t>
+          <t>318750</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>301317</t>
+          <t>299279</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>365385</t>
+          <t>362792</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>172831</t>
+          <t>172099</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>209954</t>
+          <t>209271</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>339246</t>
+          <t>339363</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>389936</t>
+          <t>391369</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>524703</t>
+          <t>525333</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>594791</t>
+          <t>594455</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,6%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>48586</t>
+          <t>49222</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>84115</t>
+          <t>85172</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>77110</t>
+          <t>75825</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>115749</t>
+          <t>112422</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>138349</t>
+          <t>134643</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>186851</t>
+          <t>191577</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>138862</t>
+          <t>136502</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>204772</t>
+          <t>204922</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>219306</t>
+          <t>220684</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>305044</t>
+          <t>305564</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>388797</t>
+          <t>393479</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>493757</t>
+          <t>496218</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>688863</t>
+          <t>709982</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1004704</t>
+          <t>1005960</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1183095</t>
+          <t>1183294</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1773963</t>
+          <t>1740240</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2020074</t>
+          <t>2029760</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2740396</t>
+          <t>2702448</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2102428</t>
+          <t>2097162</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2499050</t>
+          <t>2463670</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1515901</t>
+          <t>1533365</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2004905</t>
+          <t>2000647</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3715848</t>
+          <t>3699730</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4339960</t>
+          <t>4353458</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B1_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15551</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>25561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15404</t>
+          <t>19251</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24657</t>
+          <t>32154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>17865</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>36439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>37645</t>
+          <t>45050</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28243</t>
+          <t>34214</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50154</t>
+          <t>59769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>154549</t>
+          <t>164703</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>133114</t>
+          <t>144442</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177741</t>
+          <t>188947</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129809</t>
+          <t>143623</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114099</t>
+          <t>127059</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146837</t>
+          <t>163129</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>284358</t>
+          <t>308326</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257139</t>
+          <t>279390</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>310524</t>
+          <t>336819</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>326374</t>
+          <t>356160</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>301390</t>
+          <t>332087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>346508</t>
+          <t>378304</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289294</t>
+          <t>312513</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>272414</t>
+          <t>293282</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>306611</t>
+          <t>330779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>615668</t>
+          <t>668673</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>586374</t>
+          <t>636911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>643238</t>
+          <t>698111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>504196</t>
+          <t>549639</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504196</t>
+          <t>549639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504196</t>
+          <t>549639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>951663</t>
+          <t>1038050</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>951663</t>
+          <t>1038050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>951663</t>
+          <t>1038050</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,27 +1329,27 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9479</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23352</t>
+          <t>24852</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15527</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33264</t>
+          <t>36720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25331</t>
+          <t>27761</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17550</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37138</t>
+          <t>39113</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48683</t>
+          <t>52613</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37324</t>
+          <t>39890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62905</t>
+          <t>67073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>140056</t>
+          <t>151308</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121658</t>
+          <t>130175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161113</t>
+          <t>172722</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>132641</t>
+          <t>147555</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117021</t>
+          <t>130067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149823</t>
+          <t>166253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>272697</t>
+          <t>298863</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249759</t>
+          <t>273364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>298872</t>
+          <t>326251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>283126</t>
+          <t>300814</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>262117</t>
+          <t>278576</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>303849</t>
+          <t>323224</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>218652</t>
+          <t>241047</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>200657</t>
+          <t>222034</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>233585</t>
+          <t>259209</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>501778</t>
+          <t>541861</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>474608</t>
+          <t>513934</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>527648</t>
+          <t>570110</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>449990</t>
+          <t>480738</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>449990</t>
+          <t>480738</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>449990</t>
+          <t>480738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>381842</t>
+          <t>422397</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>381842</t>
+          <t>422397</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>381842</t>
+          <t>422397</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>831832</t>
+          <t>903135</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>831832</t>
+          <t>903135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>831832</t>
+          <t>903135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28355</t>
+          <t>30319</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49862</t>
+          <t>42525</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>15725</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20772</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>42792</t>
+          <t>46044</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>35626</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64797</t>
+          <t>59556</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>123179</t>
+          <t>141104</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49081</t>
+          <t>122855</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>202364</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>56178</t>
+          <t>63542</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47265</t>
+          <t>53506</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>74841</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>179356</t>
+          <t>204646</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67768</t>
+          <t>182719</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>262952</t>
+          <t>227521</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>508847</t>
+          <t>292295</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>408415</t>
+          <t>268329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>602657</t>
+          <t>312849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>90861</t>
+          <t>102469</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80523</t>
+          <t>90508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100310</t>
+          <t>113884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>599708</t>
+          <t>394765</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>492860</t>
+          <t>371693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>742788</t>
+          <t>420845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>64,0%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>833604</t>
+          <t>657606</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>833604</t>
+          <t>657606</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>833604</t>
+          <t>657606</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>29820</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19684</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39251</t>
+          <t>42213</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17549</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>30353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>45426</t>
+          <t>50983</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31139</t>
+          <t>39121</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58853</t>
+          <t>65887</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>65605</t>
+          <t>72970</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51119</t>
+          <t>58765</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82001</t>
+          <t>89182</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>50779</t>
+          <t>55527</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>44070</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69151</t>
+          <t>67877</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>116383</t>
+          <t>128496</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80692</t>
+          <t>109992</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>140041</t>
+          <t>149705</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>303992</t>
+          <t>341921</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>271878</t>
+          <t>308135</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>334442</t>
+          <t>377095</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>445797</t>
+          <t>272142</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>299160</t>
+          <t>250563</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>712288</t>
+          <t>297800</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>749788</t>
+          <t>614064</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>594113</t>
+          <t>573157</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1133189</t>
+          <t>654127</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>635364</t>
+          <t>685121</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>599651</t>
+          <t>649415</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>668061</t>
+          <t>719845</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>462329</t>
+          <t>510673</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>230804</t>
+          <t>484375</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>591204</t>
+          <t>533848</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1097692</t>
+          <t>1195794</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>765693</t>
+          <t>1152191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1238801</t>
+          <t>1238397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>62,25%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1032837</t>
+          <t>1129832</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1032837</t>
+          <t>1129832</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1032837</t>
+          <t>1129832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>976453</t>
+          <t>859505</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>976453</t>
+          <t>859505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>976453</t>
+          <t>859505</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2009289</t>
+          <t>1989338</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2009289</t>
+          <t>1989338</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2009289</t>
+          <t>1989338</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18278</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28105</t>
+          <t>32485</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>40783</t>
+          <t>48134</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29205</t>
+          <t>37561</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54909</t>
+          <t>61979</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>59061</t>
+          <t>70172</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44649</t>
+          <t>56392</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74479</t>
+          <t>88274</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>40667</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26180</t>
+          <t>30260</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46867</t>
+          <t>53643</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>82793</t>
+          <t>93319</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61796</t>
+          <t>79993</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100757</t>
+          <t>107909</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>118397</t>
+          <t>133986</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96171</t>
+          <t>117222</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138161</t>
+          <t>153320</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>154163</t>
+          <t>184089</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>134563</t>
+          <t>162541</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>174992</t>
+          <t>208333</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>291618</t>
+          <t>326162</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>208318</t>
+          <t>303270</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>334177</t>
+          <t>350371</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>445781</t>
+          <t>510252</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>366323</t>
+          <t>476314</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>491348</t>
+          <t>542077</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>265277</t>
+          <t>319488</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>244145</t>
+          <t>291720</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>287226</t>
+          <t>342998</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>423588</t>
+          <t>360501</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>366790</t>
+          <t>335455</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>536042</t>
+          <t>383733</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>688865</t>
+          <t>679989</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>631908</t>
+          <t>646703</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>807341</t>
+          <t>716817</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>473322</t>
+          <t>566282</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>473322</t>
+          <t>566282</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>473322</t>
+          <t>566282</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>838782</t>
+          <t>828116</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>838782</t>
+          <t>828116</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>838782</t>
+          <t>828116</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1312104</t>
+          <t>1394398</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1312104</t>
+          <t>1394398</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1312104</t>
+          <t>1394398</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,22 +3570,22 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>503</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,22 +3605,22 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>23700</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>17311</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28797</t>
+          <t>31212</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32070</t>
+          <t>34033</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>21228</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>76254</t>
+          <t>85511</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>63774</t>
+          <t>71176</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>91321</t>
+          <t>101903</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>84086</t>
+          <t>94952</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>69276</t>
+          <t>78141</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>104004</t>
+          <t>113981</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>41640</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22511</t>
+          <t>26384</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>56829</t>
+          <t>60213</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>293559</t>
+          <t>327167</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>268613</t>
+          <t>298697</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>318750</t>
+          <t>356142</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>330235</t>
+          <t>368807</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>299279</t>
+          <t>337662</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>362792</t>
+          <t>406041</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>37,71%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>194046</t>
+          <t>184154</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>172099</t>
+          <t>162990</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>209271</t>
+          <t>200280</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>365855</t>
+          <t>403257</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>339363</t>
+          <t>375102</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>391369</t>
+          <t>433136</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>559902</t>
+          <t>587411</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>525333</t>
+          <t>549110</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>594455</t>
+          <t>622445</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>756952</t>
+          <t>839635</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>756952</t>
+          <t>839635</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>756952</t>
+          <t>839635</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>997460</t>
+          <t>1076863</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>997460</t>
+          <t>1076863</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>997460</t>
+          <t>1076863</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>66311</t>
+          <t>74096</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>49222</t>
+          <t>58073</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>85172</t>
+          <t>92048</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>95827</t>
+          <t>110701</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>75825</t>
+          <t>95406</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>129696</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>162138</t>
+          <t>184797</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>134643</t>
+          <t>162699</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>191577</t>
+          <t>209875</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>176152</t>
+          <t>197500</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>136502</t>
+          <t>172965</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>204922</t>
+          <t>228183</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>271834</t>
+          <t>303642</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>220684</t>
+          <t>275324</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>305564</t>
+          <t>333379</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>447986</t>
+          <t>501142</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>393479</t>
+          <t>459661</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>496218</t>
+          <t>540920</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>912615</t>
+          <t>1024767</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>709982</t>
+          <t>964790</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1005960</t>
+          <t>1078712</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1349601</t>
+          <t>1280191</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1183294</t>
+          <t>1228838</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1740240</t>
+          <t>1328692</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2262215</t>
+          <t>2304957</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2029760</t>
+          <t>2223565</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2702448</t>
+          <t>2382934</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2213034</t>
+          <t>2138033</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2097162</t>
+          <t>2076875</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2463670</t>
+          <t>2202369</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1850580</t>
+          <t>1930460</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1533365</t>
+          <t>1876690</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2000647</t>
+          <t>1980852</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4063613</t>
+          <t>4068494</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3699730</t>
+          <t>3985309</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4353458</t>
+          <t>4157571</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3368111</t>
+          <t>3434396</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3368111</t>
+          <t>3434396</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3368111</t>
+          <t>3434396</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3567841</t>
+          <t>3624993</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3567841</t>
+          <t>3624993</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3567841</t>
+          <t>3624993</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6935952</t>
+          <t>7059390</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6935952</t>
+          <t>7059390</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6935952</t>
+          <t>7059390</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
